--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -1763,6 +1763,11 @@
           <t>La Mondotte</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Stag's Leap</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="14.5" customHeight="1">
       <c r="C50" t="inlineStr">
@@ -3414,6 +3419,11 @@
           <t>Cos d'Estournel</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Stag's Leap</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -1775,6 +1775,11 @@
           <t>Pichon Baron</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Cliff Lede Poetry</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="14.5" customHeight="1">
       <c r="C51" t="inlineStr">
@@ -3431,6 +3436,11 @@
           <t>Smith Haut Lafitte</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Cliff Lede Poetry</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1787,6 +1787,11 @@
           <t>Pontet Canet</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Macdonald</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="14.5" customHeight="1">
       <c r="C52" t="inlineStr">
@@ -1794,6 +1799,11 @@
           <t>Vieaux Chateau Certan</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Araujo Estate</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="C53" s="7" t="inlineStr">
@@ -1862,6 +1872,13 @@
       <c r="C62" t="inlineStr">
         <is>
           <t>Le Dome</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Les Carmes Haut-Brion</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="25.453125" customWidth="1" min="1" max="1"/>
@@ -3439,6 +3456,25 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>Cliff Lede Poetry</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Les Carmes Haut-Brion</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Macdonald</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Araujo Estate</t>
         </is>
       </c>
     </row>

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1879,6 +1879,13 @@
       <c r="C63" t="inlineStr">
         <is>
           <t>Les Carmes Haut-Brion</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Luciano Sandrone</t>
         </is>
       </c>
     </row>
@@ -2915,6 +2922,11 @@
           <t>Combo - Araujo + Eisele</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Luciano Sandrone</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dalla Valle</t>
+          <t>Dalla Valle Maya</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1809,6 +1809,11 @@
       <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Dyquem</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Dalla Valle</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="25.453125" customWidth="1" min="1" max="1"/>
@@ -3487,6 +3492,13 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>Araujo Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Dalla Valle Maya</t>
         </is>
       </c>
     </row>

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -1249,6 +1249,11 @@
           <t xml:space="preserve">Batailley </t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bonnes-Mares</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
       <c r="C18" s="2" t="inlineStr">
@@ -2658,6 +2663,11 @@
           <t>La Fleur Petrus</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bonnes-Mares</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Levy &amp; McClellan</t>
